--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -437,962 +437,962 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122.3696610208505</v>
+        <v>15.54531838293458</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120.2530840959018</v>
+        <v>14.66410218309929</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119.3668302616216</v>
+        <v>12.44995122914631</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118.9920177595465</v>
+        <v>7.778152495954682</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118.0340714764586</v>
+        <v>7.378868840111652</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118.0166784913146</v>
+        <v>6.700222752642359</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117.9316255663383</v>
+        <v>6.679901416981371</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115.9706916035457</v>
+        <v>6.232889988004143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113.5549757650904</v>
+        <v>6.078610417987518</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109.8483881890557</v>
+        <v>5.601896270963724</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108.5032624508837</v>
+        <v>5.245654095095698</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104.0183537709018</v>
+        <v>5.230808144247745</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103.9779436621758</v>
+        <v>5.104770821357429</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103.6147249579245</v>
+        <v>5.104767181518222</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103.5141944662491</v>
+        <v>5.0586650418178</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103.5100378161867</v>
+        <v>5.036408924477143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>100.1008992124274</v>
+        <v>5.021573723728667</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99.33879185119594</v>
+        <v>4.916023145354487</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98.61693960618288</v>
+        <v>4.904649436675812</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>98.61445422086464</v>
+        <v>4.831524459184733</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98.25972113653535</v>
+        <v>4.813943547329425</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95.65585002967177</v>
+        <v>4.736889059669469</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>94.32421554746446</v>
+        <v>4.726224018944181</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>94.17035066844453</v>
+        <v>4.722595506367155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>87.53503658362602</v>
+        <v>4.71218879506925</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>87.09682226049139</v>
+        <v>4.71218562740654</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>87.08008387620227</v>
+        <v>4.707771730101995</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>86.23053519236365</v>
+        <v>4.604259769292107</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>86.19160892051926</v>
+        <v>4.49506888472706</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>85.40926306106505</v>
+        <v>4.452265614177953</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>85.32129470414137</v>
+        <v>4.449494715575342</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>84.58861301803108</v>
+        <v>4.446725358595827</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>84.45294476330498</v>
+        <v>4.432364585717341</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>84.45173589405893</v>
+        <v>4.418143663341567</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>83.77121078265957</v>
+        <v>4.404089826112267</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>75.34986600329692</v>
+        <v>4.38829151753326</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>74.06579899191482</v>
+        <v>4.388291517533238</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>72.96743609780836</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>72.50560116949372</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>72.48730665055778</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>72.11852578992024</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>71.52752114811501</v>
+        <v>4.388291517533194</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>71.22402851834319</v>
+        <v>4.388291517533194</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>71.22207101901665</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>63.6369388034574</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>61.45952628842824</v>
+        <v>4.388291517533149</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>61.35333303061934</v>
+        <v>4.388291517533127</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>61.34729094538223</v>
+        <v>4.388291517533127</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>60.82150797854977</v>
+        <v>4.388291517533083</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>60.82078971182391</v>
+        <v>4.349633931007113</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>60.77672424253744</v>
+        <v>4.349633931007069</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>60.77423331359974</v>
+        <v>4.34963393100698</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>60.52652574704242</v>
+        <v>4.325966886632271</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>60.51563644296317</v>
+        <v>4.274519009916911</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>59.48819672008609</v>
+        <v>4.270257231299013</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>58.91979468833282</v>
+        <v>4.23344250423825</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>56.96959454940236</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>56.8837727817519</v>
+        <v>4.233442504238205</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>56.4772624158752</v>
+        <v>4.233442504238205</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>56.47643679988512</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>56.39963746903088</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>55.84715533812479</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>55.84632666870497</v>
+        <v>4.233442504238161</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>55.57355927847324</v>
+        <v>4.219071160432186</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>55.52180975023741</v>
+        <v>4.19406792021233</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>55.50170466062591</v>
+        <v>4.175848843858931</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>55.29179503502263</v>
+        <v>4.168259217128245</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>55.29095509161613</v>
+        <v>4.16099973736932</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>55.24927688633537</v>
+        <v>4.152707281016244</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>55.04328306310995</v>
+        <v>4.139113523896243</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>54.91491015618109</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>53.59858580102114</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>52.3448589922348</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>52.34426192459142</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>52.09107794647971</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>52.09049282588706</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>51.6460718937924</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>51.09995909409491</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>51.09985036293892</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>51.00566202934783</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>51.0038272970389</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>50.87989176062561</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>50.7247218236779</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>50.71446769206425</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>50.58962627834663</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>49.95846814405213</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>49.91012341200959</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>49.59272401751318</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>49.3136830778272</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>48.99442442520443</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>48.81253722345948</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>48.81113549548445</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>48.3856912111647</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>48.24474675373118</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>48.21518825939027</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>47.3828327212194</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>47.16378256687458</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>47.14989648325469</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>46.75876632078128</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>46.75771388504547</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>46.73572992304257</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>46.73360539542289</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>46.7221839859568</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>46.71215201428696</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>46.66778145414288</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>46.20529802361622</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>46.19260418339047</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>46.18757613860151</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>46.18685288297866</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>46.08306903151487</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>46.06721127675289</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>46.06570815208594</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>46.00416260795986</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>45.88489854387943</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>45.88416495531743</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>45.61576319174895</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>45.50513268808658</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>45.40697296102315</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>45.39065198621006</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>44.98479329875995</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>44.97209918171004</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>44.83226435125977</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>44.81870654010052</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>44.78666419603462</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>44.77634188067296</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>44.27975738195504</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>44.27204698126776</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>44.13756178852925</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>43.85408607987592</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>43.84752562644493</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>43.71091207231369</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>43.71003321564334</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>43.57349490266771</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>42.3612752439641</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>42.19382281025711</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>42.1931241884006</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>42.13673871869489</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>41.77982935106288</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>41.68368550040984</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>41.68298210999572</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>41.38222007483981</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>41.38144605294234</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>41.24582692493893</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>40.73037655793892</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>40.72964389977154</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>40.61581323795715</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>40.44517200785226</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>40.44444765314761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>39.57848048119877</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>39.00318136266564</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>38.08866383316067</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>37.60946163756174</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>37.59002305336626</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>37.47972346400194</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>37.45435129715281</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>37.20060413702405</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>37.19849601747077</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>37.17564367290004</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>37.17491253687244</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>36.73584471376986</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>36.7353276646313</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>35.92621294205117</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>35.31170927063887</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>35.25492902591268</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>35.24838351237778</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>35.13778422663728</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>35.12786997630884</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>34.87741175950251</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>34.80423891459146</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>34.79863853649483</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>34.22661373716899</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>34.12895930269107</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>34.12774421803679</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>33.6332276956378</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>33.28616831621833</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>33.28494992526429</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>33.22985051122621</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>32.92286458542477</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>32.8359830036208</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>32.83476755355916</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>32.83319330635717</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>32.83258138116746</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>32.70594636993432</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>32.49022475613583</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>32.34833898852064</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>32.03085661431304</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>32.03018088652498</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>31.99322646477615</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>31.89705472813002</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>31.89641703987679</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>31.89424898727441</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>31.89361832582316</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="194">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,1446 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>17.36819739724094</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13.35221755990217</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10.40744226314052</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8.799274107140009</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8.240447025363707</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4.698819438089386</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4.480258734680631</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,1446 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>26.05845476919577</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>24.30731921307373</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>18.83187548348985</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>18.6144625992209</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>17.36819739724094</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13.35221755990217</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>10.40744226314052</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9.500031717086577</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8.799274107140009</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8.240447025363707</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8.216112360289962</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7.788605641411117</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6.338943322872359</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5.041536772765931</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4.952326044590071</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4.91891351310707</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4.916017807544404</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4.906387217104968</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4.698819438089386</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4.685687162808527</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4.480258734680631</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -1,37 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>Fitness</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +57,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,22 +373,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Fitness</t>
-        </is>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -382,6 +382,1446 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>18.6144625992209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -384,62 +384,62 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2">
-        <v>18.6144625992209</v>
+        <v>17.36819739724094</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3">
-        <v>17.02360507988341</v>
+        <v>15.77900665531947</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4">
-        <v>16.55407615166203</v>
+        <v>15.54531838293443</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5">
-        <v>15.77900665531947</v>
+        <v>14.66410218309929</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6">
-        <v>14.66410218309929</v>
+        <v>13.3447267903799</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7">
-        <v>13.3447267903799</v>
+        <v>12.44995122914663</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8">
-        <v>12.44995122914663</v>
+        <v>8.335508550897774</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9">
-        <v>7.665195775008982</v>
+        <v>7.778152495954949</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10">
-        <v>7.542073792847603</v>
+        <v>7.665195775008982</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>7.251568631278382</v>
+        <v>7.542073792847603</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>7.024423915842871</v>
+        <v>7.378868840111763</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>6.73650542439198</v>
+        <v>7.024423915842871</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -484,32 +484,32 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>5.104770821357563</v>
+        <v>5.230808144247701</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23">
-        <v>5.0586650418176</v>
+        <v>5.104770821357563</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24">
-        <v>5.03640892447712</v>
+        <v>5.104767181518222</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25">
-        <v>5.021573723728667</v>
+        <v>5.03640892447712</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>4.924888436226138</v>
+        <v>5.021573723728667</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>4.916023145354398</v>
+        <v>4.924888436226138</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -589,62 +589,62 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>4.46061635483932</v>
+        <v>4.49506888472706</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>4.452269003190468</v>
+        <v>4.46061635483932</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>4.452265614177953</v>
+        <v>4.452695169918464</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>4.449494715575342</v>
+        <v>4.452269003190468</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47">
-        <v>4.446725358595827</v>
+        <v>4.452265614177953</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48">
-        <v>4.418143663341567</v>
+        <v>4.449494715575342</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49">
-        <v>4.404089826112356</v>
+        <v>4.446725358595827</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50">
-        <v>4.38829151753326</v>
+        <v>4.432364585717341</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51">
-        <v>4.388291517533238</v>
+        <v>4.418143663341567</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52">
-        <v>4.388291517533216</v>
+        <v>4.404089826112356</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53">
-        <v>4.388291517533216</v>
+        <v>4.388291517533238</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54">
-        <v>4.388291517533216</v>
+        <v>4.388291517533238</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -654,12 +654,12 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56">
-        <v>4.388291517533194</v>
+        <v>4.388291517533216</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57">
-        <v>4.388291517533194</v>
+        <v>4.388291517533172</v>
       </c>
     </row>
     <row r="58" spans="1:1">
@@ -679,47 +679,47 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61">
-        <v>4.388291517533172</v>
+        <v>4.388291517533149</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62">
-        <v>4.388291517533172</v>
+        <v>4.388291517533127</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63">
-        <v>4.388291517533172</v>
+        <v>4.349633931007113</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64">
-        <v>4.388291517533172</v>
+        <v>4.349633931007091</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
-        <v>4.388291517533172</v>
+        <v>4.349633931007069</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66">
-        <v>4.388291517533149</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67">
-        <v>4.388291517533127</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>4.349633931007113</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>4.349633931007091</v>
+        <v>4.349633931007046</v>
       </c>
     </row>
     <row r="70" spans="1:1">
@@ -739,7 +739,7 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73">
-        <v>4.349633931007046</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -749,47 +749,47 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>4.34963393100698</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>4.34963393100698</v>
+        <v>4.349633931007024</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>4.335475298823388</v>
+        <v>4.349633931007002</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>4.325966886632249</v>
+        <v>4.34963393100698</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>4.270257231299013</v>
+        <v>4.34963393100698</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>4.23344250423825</v>
+        <v>4.335475298823388</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>4.233442504238227</v>
+        <v>4.325966886632249</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>4.233442504238227</v>
+        <v>4.270257231299013</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83">
-        <v>4.233442504238227</v>
+        <v>4.23344250423825</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -799,112 +799,112 @@
     </row>
     <row r="85" spans="1:1">
       <c r="A85">
-        <v>4.233442504238183</v>
+        <v>4.233442504238227</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86">
-        <v>4.233442504238161</v>
+        <v>4.233442504238205</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87">
-        <v>4.233442504238139</v>
+        <v>4.233442504238205</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88">
-        <v>4.233442504238139</v>
+        <v>4.233442504238183</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>4.233442504238094</v>
+        <v>4.233442504238161</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>4.194067920212374</v>
+        <v>4.233442504238139</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>4.175848843858931</v>
+        <v>4.233442504238139</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
-        <v>4.169529680102513</v>
+        <v>4.233442504238116</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
-        <v>4.16099973736932</v>
+        <v>4.233442504238094</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
-        <v>4.152707281016221</v>
+        <v>4.194067920212374</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
-        <v>4.139113523896243</v>
+        <v>4.175848843858931</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
-        <v>4.11804620363041</v>
+        <v>4.169529680102513</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
-        <v>4.061116337551218</v>
+        <v>4.168259217128245</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98">
-        <v>4.00797224759124</v>
+        <v>4.16099973736932</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99">
-        <v>4.000000000000048</v>
+        <v>4.152707281016221</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100">
-        <v>4.000000000000048</v>
+        <v>4.139113523896243</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101">
-        <v>4.000000000000048</v>
+        <v>4.11804620363041</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102">
-        <v>4.000000000000026</v>
+        <v>4.061116337551218</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103">
-        <v>4.000000000000026</v>
+        <v>4.00797224759124</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104">
-        <v>4.000000000000026</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105">
-        <v>4.000000000000026</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106">
-        <v>4.000000000000026</v>
+        <v>4.000000000000048</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -939,22 +939,22 @@
     </row>
     <row r="113" spans="1:1">
       <c r="A113">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116">
-        <v>4.000000000000004</v>
+        <v>4.000000000000026</v>
       </c>
     </row>
     <row r="117" spans="1:1">
@@ -1004,22 +1004,22 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129">
-        <v>3.999999999999981</v>
+        <v>4.000000000000004</v>
       </c>
     </row>
     <row r="130" spans="1:1">
@@ -1059,22 +1059,22 @@
     </row>
     <row r="137" spans="1:1">
       <c r="A137">
-        <v>3.999999999999959</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138">
-        <v>3.999999999999959</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139">
-        <v>3.999999999999959</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140">
-        <v>3.999999999999959</v>
+        <v>3.999999999999981</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -1089,12 +1089,12 @@
     </row>
     <row r="143" spans="1:1">
       <c r="A143">
-        <v>3.999999999999937</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144">
-        <v>3.999999999999937</v>
+        <v>3.999999999999959</v>
       </c>
     </row>
     <row r="145" spans="1:1">
@@ -1104,17 +1104,17 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146">
-        <v>-1</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147">
-        <v>-1</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148">
-        <v>-1</v>
+        <v>3.999999999999937</v>
       </c>
     </row>
     <row r="149" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -382,6 +382,1446 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>24.30731921307373</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>21.64736113255699</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>18.83187548348985</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>17.36819739724094</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>4.952326044590071</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>4.91891351310707</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -382,6 +382,1446 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>26.05845476919577</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>24.30731921307373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>18.83187548348985</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>18.6144625992209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>17.36819739724094</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>13.35221755990217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>11.45377185083114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>10.65512917904204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>10.40744226314052</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>9.500031717086577</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>8.913627025534243</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>8.799274107140009</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>8.254373206547704</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>8.240447025363707</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>8.216112360289962</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>7.788605641411117</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>6.338943322872359</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>5.041536772765931</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>4.952326044590071</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>4.91891351310707</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>4.916017807544404</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>4.906387217104968</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>4.795308242662988</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>4.736883734731001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>4.698819438089386</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>4.685687162808527</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>4.480258734680631</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>4.429826105328005</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -382,6 +382,1446 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>26.05845476919577</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>24.30731921307373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>22.86600961511795</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>18.83187548348985</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>18.6144625992209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>17.36819739724094</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>11.45377185083114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>10.65512917904204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>10.40744226314052</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>9.500031717086577</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>9.16181601832664</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>8.913627025534243</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>8.254373206547704</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>8.240447025363707</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>8.216112360289962</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>7.788605641411117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>6.338943322872359</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>5.041536772765931</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>4.952326044590071</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>4.91891351310707</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>4.916017807544404</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>4.906387217104968</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>4.795308242662988</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>4.736883734731001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>4.698819438089386</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>4.685687162808527</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>4.480258734680631</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>4.429826105328005</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -382,6 +382,1446 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>17.36819739724094</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>13.35221755990217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>10.40744226314052</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>9.500031717086577</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>8.913627025534243</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>8.240447025363707</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>8.216112360289962</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>6.338943322872359</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>4.906387217104968</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>4.698819438089386</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>4.685687162808527</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>4.480258734680631</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -382,6 +382,1446 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>21.64736113255699</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>17.02360507988341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>16.55407615166203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>16.43512253136544</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>15.77900665531947</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>15.54531838293443</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>13.3447267903799</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>12.44995122914663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>9.500031717086577</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>9.16181601832664</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>8.913627025534243</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>8.335508550897774</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>8.275535183571348</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>8.254373206547704</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>7.908005312866873</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>7.788605641411117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>7.778152495954949</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>7.665195775008982</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>7.378868840111763</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>7.024423915842871</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>6.73650542439198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>6.700222752642437</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>6.679901416981259</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>6.633690869228259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>6.297195687874957</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>6.232889988004087</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>6.078610417987607</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>5.601896270963658</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>5.288815940683255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>5.230808144247701</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>5.104770821357563</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>5.0586650418176</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>5.041536772765931</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>5.03640892447712</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>4.916023145354398</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>4.916017807544404</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>4.906387217104968</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>4.888685947150639</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>4.831524459184755</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>4.813943547329447</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>4.795308242662988</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>4.736889059669314</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>4.736883734731001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>4.719857205414435</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>4.712185627406562</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>4.70926335620534</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>4.685691472398901</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>4.685687162808527</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>4.669201329720174</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>4.604261815148591</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>4.604259769292196</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>4.480265097013403</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>4.475571792297295</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>4.452269003190468</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>4.44672724950923</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>4.404089826112356</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>4.349633931007091</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>4.335477316788561</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>4.335475298823388</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>4.325966886632249</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>4.254097306094673</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>4.233442504238094</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>4.194067920212374</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>4.168261095111214</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>4.152707281016221</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>4.11804620363041</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>4.061116337551218</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -374,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -382,6 +382,1446 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>26.05845476919577</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>22.86600961511792</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>21.64736113255658</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>18.83187548348985</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>18.6144625992209</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>17.36819739724091</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>17.02360507988355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
+        <v>16.43512253136529</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10">
+        <v>15.77900665531933</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11">
+        <v>15.54531838293458</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12">
+        <v>14.66410218309929</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13">
+        <v>13.34472679038015</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14">
+        <v>12.44995122914631</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15">
+        <v>10.4074422631405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16">
+        <v>8.799274107140009</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>8.335508550897641</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>8.275535183571336</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>8.254373206547704</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>8.240447025363673</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>8.216112360290072</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>7.908005312866829</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>7.788605641411217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>7.778152495954682</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>7.665195775009115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>7.542073792847603</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>7.378868840111652</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>7.251568631278382</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>7.100437277068083</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>7.024423915842903</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>6.736505424391948</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>6.700222752642359</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>6.679901416981371</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>6.338943322872459</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>6.29719568787478</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>6.232889988004143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>6.078610417987518</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>6.073739126008116</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>5.601896270963724</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>5.288815940683134</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>5.245654095095698</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>5.230808144247745</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>5.104770821357429</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>5.104767181518222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>5.0586650418178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>5.041536772765931</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>5.036408924477143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>5.021573723728667</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>4.952326044589961</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>4.924888436226138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>4.91891351310707</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>4.916023145354487</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>4.916017807544493</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>4.904649436675812</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>4.888685947150706</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>4.831524459184733</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>4.814396056529979</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>4.813943547329425</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>4.795308242662988</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>4.736889059669469</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>4.736883734731001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>4.726224018944181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>4.722595506367155</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>4.719857205414479</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>4.71218879506925</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>4.71218562740654</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>4.707771730101995</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>4.698819438089386</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>4.687572527072725</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>4.685691472398834</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>4.66920132972013</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>4.604261815148569</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>4.604259769292107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>4.49506888472706</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>4.480265097013536</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>4.480258734680609</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>4.475571792297273</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>4.46061635483932</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>4.452695169918464</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>4.452269003190423</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>4.452265614177953</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>4.449494715575342</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>4.446725358595827</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>4.432364585717341</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>4.418143663341567</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>4.404089826112267</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>4.38829151753326</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>4.388291517533238</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>4.388291517533216</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>4.388291517533194</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>4.388291517533172</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>4.388291517533149</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>4.388291517533127</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>4.388291517533105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>4.388291517533105</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>4.388291517533083</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>4.349633931007135</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>4.349633931007135</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>4.349633931007113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>4.349633931007069</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>4.349633931007046</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>4.349633931007024</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>4.349633931007002</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>4.34963393100698</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>4.349633931006958</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>4.335477316788694</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>4.335475298823366</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>4.325966886632271</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>4.274519009916911</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>4.270257231299013</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>4.254097306094806</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>4.23344250423825</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>4.233442504238227</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>4.233442504238205</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>4.233442504238183</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>4.233442504238161</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>4.233442504238139</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>4.233442504238116</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>4.219071160432186</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>4.219070660454505</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>4.19406792021233</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>4.175848843858931</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>4.169529680102513</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>4.168261095111125</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>4.168259217128245</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>4.16099973736932</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>4.152707281016244</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>4.139113523896243</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>4.118046203630454</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>4.061116337551307</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>4.00797224759124</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>4.00000000000007</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>4.000000000000048</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>4.000000000000026</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>4.000000000000004</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>3.999999999999981</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>3.999999999999959</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>3.999999999999937</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -444,17 +444,17 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -504,17 +504,17 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>0.2878201463827668</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -744,17 +744,17 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>1.127766143616094</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -774,17 +774,17 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>-1</v>
+        <v>2.416593574757897</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -819,17 +819,17 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>-1</v>
+        <v>2.416593574757864</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -1119,17 +1119,17 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="152" spans="1:1">
@@ -1164,17 +1164,17 @@
     </row>
     <row r="158" spans="1:1">
       <c r="A158">
-        <v>1.407745272749672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="161" spans="1:1">
@@ -1284,17 +1284,17 @@
     </row>
     <row r="182" spans="1:1">
       <c r="A182">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:1">
@@ -1989,17 +1989,17 @@
     </row>
     <row r="323" spans="1:1">
       <c r="A323">
-        <v>-1</v>
+        <v>2.416593574757842</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324">
-        <v>-1</v>
+        <v>0.2923395194491474</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:1">
@@ -2349,17 +2349,17 @@
     </row>
     <row r="395" spans="1:1">
       <c r="A395">
-        <v>-1</v>
+        <v>2.416593574757875</v>
       </c>
     </row>
     <row r="396" spans="1:1">
       <c r="A396">
-        <v>-1</v>
+        <v>0.2923395424601405</v>
       </c>
     </row>
     <row r="397" spans="1:1">
       <c r="A397">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398" spans="1:1">
@@ -6159,17 +6159,17 @@
     </row>
     <row r="1157" spans="1:1">
       <c r="A1157">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="1158" spans="1:1">
       <c r="A1158">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1159" spans="1:1">
       <c r="A1159">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1160" spans="1:1">
@@ -12024,17 +12024,17 @@
     </row>
     <row r="2330" spans="1:1">
       <c r="A2330">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2331" spans="1:1">
       <c r="A2331">
-        <v>0.2888776924153125</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2332" spans="1:1">
       <c r="A2332">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2333" spans="1:1">
@@ -12639,17 +12639,17 @@
     </row>
     <row r="2453" spans="1:1">
       <c r="A2453">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2454" spans="1:1">
       <c r="A2454">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2455" spans="1:1">
       <c r="A2455">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2456" spans="1:1">
@@ -23424,32 +23424,32 @@
     </row>
     <row r="4610" spans="1:1">
       <c r="A4610">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="4611" spans="1:1">
       <c r="A4611">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4612" spans="1:1">
       <c r="A4612">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4613" spans="1:1">
       <c r="A4613">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4614" spans="1:1">
       <c r="A4614">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4615" spans="1:1">
       <c r="A4615">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4616" spans="1:1">
@@ -26304,17 +26304,17 @@
     </row>
     <row r="5186" spans="1:1">
       <c r="A5186">
-        <v>-1</v>
+        <v>1.127766143616082</v>
       </c>
     </row>
     <row r="5187" spans="1:1">
       <c r="A5187">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5188" spans="1:1">
       <c r="A5188">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5189" spans="1:1">
@@ -32064,17 +32064,17 @@
     </row>
     <row r="6338" spans="1:1">
       <c r="A6338">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="6339" spans="1:1">
       <c r="A6339">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6340" spans="1:1">
       <c r="A6340">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6341" spans="1:1">
@@ -32244,17 +32244,17 @@
     </row>
     <row r="6374" spans="1:1">
       <c r="A6374">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6375" spans="1:1">
       <c r="A6375">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6376" spans="1:1">
       <c r="A6376">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6377" spans="1:1">
@@ -33684,17 +33684,17 @@
     </row>
     <row r="6662" spans="1:1">
       <c r="A6662">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6663" spans="1:1">
       <c r="A6663">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6664" spans="1:1">
       <c r="A6664">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6665" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -459,17 +459,17 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>-1</v>
+        <v>2.416593574757919</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -564,17 +564,17 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -819,17 +819,17 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>2.416593574757864</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="92" spans="1:1">
@@ -1284,17 +1284,17 @@
     </row>
     <row r="182" spans="1:1">
       <c r="A182">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="185" spans="1:1">
@@ -1479,17 +1479,17 @@
     </row>
     <row r="221" spans="1:1">
       <c r="A221">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:1">
@@ -1839,17 +1839,17 @@
     </row>
     <row r="293" spans="1:1">
       <c r="A293">
-        <v>-1</v>
+        <v>1.407745272749761</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:1">
@@ -1989,17 +1989,17 @@
     </row>
     <row r="323" spans="1:1">
       <c r="A323">
-        <v>2.416593574757842</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324">
-        <v>0.2923395194491474</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="326" spans="1:1">
@@ -2349,17 +2349,17 @@
     </row>
     <row r="395" spans="1:1">
       <c r="A395">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="396" spans="1:1">
       <c r="A396">
-        <v>0.2923395424601405</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="397" spans="1:1">
       <c r="A397">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="398" spans="1:1">
@@ -2559,17 +2559,17 @@
     </row>
     <row r="437" spans="1:1">
       <c r="A437">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439" spans="1:1">
       <c r="A439">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440" spans="1:1">
@@ -2919,17 +2919,17 @@
     </row>
     <row r="509" spans="1:1">
       <c r="A509">
-        <v>-1</v>
+        <v>1.407745272749683</v>
       </c>
     </row>
     <row r="510" spans="1:1">
       <c r="A510">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="511" spans="1:1">
       <c r="A511">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="512" spans="1:1">
@@ -3279,17 +3279,17 @@
     </row>
     <row r="581" spans="1:1">
       <c r="A581">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="582" spans="1:1">
       <c r="A582">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="583" spans="1:1">
       <c r="A583">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="584" spans="1:1">
@@ -9024,17 +9024,17 @@
     </row>
     <row r="1730" spans="1:1">
       <c r="A1730">
-        <v>1.127766143615994</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1731" spans="1:1">
       <c r="A1731">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1732" spans="1:1">
       <c r="A1732">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1733" spans="1:1">
@@ -11919,17 +11919,17 @@
     </row>
     <row r="2309" spans="1:1">
       <c r="A2309">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2310" spans="1:1">
       <c r="A2310">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2311" spans="1:1">
       <c r="A2311">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2312" spans="1:1">
@@ -12174,17 +12174,17 @@
     </row>
     <row r="2360" spans="1:1">
       <c r="A2360">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="2361" spans="1:1">
       <c r="A2361">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2362" spans="1:1">
       <c r="A2362">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2363" spans="1:1">
@@ -17664,17 +17664,17 @@
     </row>
     <row r="3458" spans="1:1">
       <c r="A3458">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="3459" spans="1:1">
       <c r="A3459">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3460" spans="1:1">
       <c r="A3460">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3461" spans="1:1">
@@ -17754,17 +17754,17 @@
     </row>
     <row r="3476" spans="1:1">
       <c r="A3476">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="3477" spans="1:1">
       <c r="A3477">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3478" spans="1:1">
       <c r="A3478">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3479" spans="1:1">
@@ -32064,17 +32064,17 @@
     </row>
     <row r="6338" spans="1:1">
       <c r="A6338">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6339" spans="1:1">
       <c r="A6339">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6340" spans="1:1">
       <c r="A6340">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6341" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -429,17 +429,17 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -459,32 +459,32 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>2.416593574757919</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -564,17 +564,17 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -774,17 +774,17 @@
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>2.416593574757897</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="83" spans="1:1">
@@ -1479,17 +1479,17 @@
     </row>
     <row r="221" spans="1:1">
       <c r="A221">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="224" spans="1:1">
@@ -2559,17 +2559,17 @@
     </row>
     <row r="437" spans="1:1">
       <c r="A437">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="439" spans="1:1">
       <c r="A439">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="440" spans="1:1">
@@ -2919,17 +2919,17 @@
     </row>
     <row r="509" spans="1:1">
       <c r="A509">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="510" spans="1:1">
       <c r="A510">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="511" spans="1:1">
       <c r="A511">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="512" spans="1:1">
@@ -3279,17 +3279,17 @@
     </row>
     <row r="581" spans="1:1">
       <c r="A581">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="582" spans="1:1">
       <c r="A582">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="583" spans="1:1">
       <c r="A583">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="584" spans="1:1">
@@ -3459,17 +3459,17 @@
     </row>
     <row r="617" spans="1:1">
       <c r="A617">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="618" spans="1:1">
       <c r="A618">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="619" spans="1:1">
       <c r="A619">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="620" spans="1:1">
@@ -6159,32 +6159,32 @@
     </row>
     <row r="1157" spans="1:1">
       <c r="A1157">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1158" spans="1:1">
       <c r="A1158">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1159" spans="1:1">
       <c r="A1159">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1160" spans="1:1">
       <c r="A1160">
-        <v>-1</v>
+        <v>2.416593574757819</v>
       </c>
     </row>
     <row r="1161" spans="1:1">
       <c r="A1161">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1162" spans="1:1">
       <c r="A1162">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1163" spans="1:1">
@@ -12174,17 +12174,17 @@
     </row>
     <row r="2360" spans="1:1">
       <c r="A2360">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2361" spans="1:1">
       <c r="A2361">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2362" spans="1:1">
       <c r="A2362">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2363" spans="1:1">
@@ -12624,17 +12624,17 @@
     </row>
     <row r="2450" spans="1:1">
       <c r="A2450">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="2451" spans="1:1">
       <c r="A2451">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2452" spans="1:1">
       <c r="A2452">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2453" spans="1:1">
@@ -12669,17 +12669,17 @@
     </row>
     <row r="2459" spans="1:1">
       <c r="A2459">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="2460" spans="1:1">
       <c r="A2460">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2461" spans="1:1">
       <c r="A2461">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2462" spans="1:1">
@@ -17664,17 +17664,17 @@
     </row>
     <row r="3458" spans="1:1">
       <c r="A3458">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3459" spans="1:1">
       <c r="A3459">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3460" spans="1:1">
       <c r="A3460">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3461" spans="1:1">
@@ -17754,17 +17754,17 @@
     </row>
     <row r="3476" spans="1:1">
       <c r="A3476">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3477" spans="1:1">
       <c r="A3477">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3478" spans="1:1">
       <c r="A3478">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3479" spans="1:1">
@@ -23424,17 +23424,17 @@
     </row>
     <row r="4610" spans="1:1">
       <c r="A4610">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4611" spans="1:1">
       <c r="A4611">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4612" spans="1:1">
       <c r="A4612">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4613" spans="1:1">
@@ -25239,17 +25239,17 @@
     </row>
     <row r="4973" spans="1:1">
       <c r="A4973">
-        <v>-1</v>
+        <v>1.407745272749772</v>
       </c>
     </row>
     <row r="4974" spans="1:1">
       <c r="A4974">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4975" spans="1:1">
       <c r="A4975">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4976" spans="1:1">
@@ -26304,17 +26304,17 @@
     </row>
     <row r="5186" spans="1:1">
       <c r="A5186">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5187" spans="1:1">
       <c r="A5187">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5188" spans="1:1">
       <c r="A5188">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5189" spans="1:1">
@@ -26859,17 +26859,17 @@
     </row>
     <row r="5297" spans="1:1">
       <c r="A5297">
-        <v>-1</v>
+        <v>1.407745272749761</v>
       </c>
     </row>
     <row r="5298" spans="1:1">
       <c r="A5298">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5299" spans="1:1">
       <c r="A5299">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5300" spans="1:1">
@@ -28119,17 +28119,17 @@
     </row>
     <row r="5549" spans="1:1">
       <c r="A5549">
-        <v>-1</v>
+        <v>1.40774527274965</v>
       </c>
     </row>
     <row r="5550" spans="1:1">
       <c r="A5550">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5551" spans="1:1">
       <c r="A5551">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5552" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -429,17 +429,17 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -474,17 +474,17 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -564,17 +564,17 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -3459,17 +3459,17 @@
     </row>
     <row r="617" spans="1:1">
       <c r="A617">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="618" spans="1:1">
       <c r="A618">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="619" spans="1:1">
       <c r="A619">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="620" spans="1:1">
@@ -9039,17 +9039,17 @@
     </row>
     <row r="1733" spans="1:1">
       <c r="A1733">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="1734" spans="1:1">
       <c r="A1734">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1735" spans="1:1">
       <c r="A1735">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1736" spans="1:1">
@@ -12624,17 +12624,17 @@
     </row>
     <row r="2450" spans="1:1">
       <c r="A2450">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2451" spans="1:1">
       <c r="A2451">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2452" spans="1:1">
       <c r="A2452">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2453" spans="1:1">
@@ -12669,17 +12669,17 @@
     </row>
     <row r="2459" spans="1:1">
       <c r="A2459">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2460" spans="1:1">
       <c r="A2460">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2461" spans="1:1">
       <c r="A2461">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2462" spans="1:1">
@@ -15249,17 +15249,17 @@
     </row>
     <row r="2975" spans="1:1">
       <c r="A2975">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="2976" spans="1:1">
       <c r="A2976">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2977" spans="1:1">
       <c r="A2977">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2978" spans="1:1">
@@ -24564,17 +24564,17 @@
     </row>
     <row r="4838" spans="1:1">
       <c r="A4838">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="4839" spans="1:1">
       <c r="A4839">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4840" spans="1:1">
       <c r="A4840">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4841" spans="1:1">
@@ -25239,17 +25239,17 @@
     </row>
     <row r="4973" spans="1:1">
       <c r="A4973">
-        <v>1.407745272749772</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4974" spans="1:1">
       <c r="A4974">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4975" spans="1:1">
       <c r="A4975">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4976" spans="1:1">
@@ -25599,17 +25599,17 @@
     </row>
     <row r="5045" spans="1:1">
       <c r="A5045">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="5046" spans="1:1">
       <c r="A5046">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5047" spans="1:1">
       <c r="A5047">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5048" spans="1:1">
@@ -26859,17 +26859,17 @@
     </row>
     <row r="5297" spans="1:1">
       <c r="A5297">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5298" spans="1:1">
       <c r="A5298">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5299" spans="1:1">
       <c r="A5299">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5300" spans="1:1">
@@ -28119,17 +28119,17 @@
     </row>
     <row r="5549" spans="1:1">
       <c r="A5549">
-        <v>1.40774527274965</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5550" spans="1:1">
       <c r="A5550">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5551" spans="1:1">
       <c r="A5551">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5552" spans="1:1">
@@ -36084,17 +36084,17 @@
     </row>
     <row r="7142" spans="1:1">
       <c r="A7142">
-        <v>-1</v>
+        <v>1.407745272749761</v>
       </c>
     </row>
     <row r="7143" spans="1:1">
       <c r="A7143">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7144" spans="1:1">
       <c r="A7144">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7145" spans="1:1">
@@ -38334,17 +38334,17 @@
     </row>
     <row r="7592" spans="1:1">
       <c r="A7592">
-        <v>-1</v>
+        <v>1.407745272749739</v>
       </c>
     </row>
     <row r="7593" spans="1:1">
       <c r="A7593">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7594" spans="1:1">
       <c r="A7594">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7595" spans="1:1">
@@ -39054,17 +39054,17 @@
     </row>
     <row r="7736" spans="1:1">
       <c r="A7736">
-        <v>-1</v>
+        <v>1.407745272749727</v>
       </c>
     </row>
     <row r="7737" spans="1:1">
       <c r="A7737">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7738" spans="1:1">
       <c r="A7738">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7739" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -504,17 +504,17 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>-1</v>
+        <v>2.416593574757875</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>-1</v>
+        <v>0.2878201463827668</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -564,17 +564,17 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -744,17 +744,17 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>-1</v>
+        <v>1.127766143616094</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -1464,17 +1464,17 @@
     </row>
     <row r="218" spans="1:1">
       <c r="A218">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221" spans="1:1">
@@ -1839,17 +1839,17 @@
     </row>
     <row r="293" spans="1:1">
       <c r="A293">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="296" spans="1:1">
@@ -3279,17 +3279,17 @@
     </row>
     <row r="581" spans="1:1">
       <c r="A581">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="582" spans="1:1">
       <c r="A582">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="583" spans="1:1">
       <c r="A583">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="584" spans="1:1">
@@ -6159,32 +6159,32 @@
     </row>
     <row r="1157" spans="1:1">
       <c r="A1157">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="1158" spans="1:1">
       <c r="A1158">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1159" spans="1:1">
       <c r="A1159">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1160" spans="1:1">
       <c r="A1160">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1161" spans="1:1">
       <c r="A1161">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1162" spans="1:1">
       <c r="A1162">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1163" spans="1:1">
@@ -12159,17 +12159,17 @@
     </row>
     <row r="2357" spans="1:1">
       <c r="A2357">
-        <v>-1</v>
+        <v>2.416593574757853</v>
       </c>
     </row>
     <row r="2358" spans="1:1">
       <c r="A2358">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2359" spans="1:1">
       <c r="A2359">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2360" spans="1:1">
@@ -15249,17 +15249,17 @@
     </row>
     <row r="2975" spans="1:1">
       <c r="A2975">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2976" spans="1:1">
       <c r="A2976">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2977" spans="1:1">
       <c r="A2977">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2978" spans="1:1">
@@ -23439,17 +23439,17 @@
     </row>
     <row r="4613" spans="1:1">
       <c r="A4613">
-        <v>-1</v>
+        <v>1.407745272749739</v>
       </c>
     </row>
     <row r="4614" spans="1:1">
       <c r="A4614">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4615" spans="1:1">
       <c r="A4615">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4616" spans="1:1">
@@ -24564,17 +24564,17 @@
     </row>
     <row r="4838" spans="1:1">
       <c r="A4838">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4839" spans="1:1">
       <c r="A4839">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4840" spans="1:1">
       <c r="A4840">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4841" spans="1:1">
@@ -24864,17 +24864,17 @@
     </row>
     <row r="4898" spans="1:1">
       <c r="A4898">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="4899" spans="1:1">
       <c r="A4899">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4900" spans="1:1">
       <c r="A4900">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4901" spans="1:1">
@@ -25599,17 +25599,17 @@
     </row>
     <row r="5045" spans="1:1">
       <c r="A5045">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5046" spans="1:1">
       <c r="A5046">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5047" spans="1:1">
       <c r="A5047">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5048" spans="1:1">
@@ -36084,17 +36084,17 @@
     </row>
     <row r="7142" spans="1:1">
       <c r="A7142">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7143" spans="1:1">
       <c r="A7143">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7144" spans="1:1">
       <c r="A7144">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7145" spans="1:1">
@@ -38334,17 +38334,17 @@
     </row>
     <row r="7592" spans="1:1">
       <c r="A7592">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7593" spans="1:1">
       <c r="A7593">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7594" spans="1:1">
       <c r="A7594">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7595" spans="1:1">
@@ -39054,17 +39054,17 @@
     </row>
     <row r="7736" spans="1:1">
       <c r="A7736">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7737" spans="1:1">
       <c r="A7737">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7738" spans="1:1">
       <c r="A7738">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7739" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -474,17 +474,17 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -504,17 +504,17 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>0.2878201463827668</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -744,17 +744,17 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>1.127766143616094</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -1464,17 +1464,17 @@
     </row>
     <row r="218" spans="1:1">
       <c r="A218">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="221" spans="1:1">
@@ -1539,17 +1539,17 @@
     </row>
     <row r="233" spans="1:1">
       <c r="A233">
-        <v>-1</v>
+        <v>2.416593574757875</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:1">
@@ -3279,17 +3279,17 @@
     </row>
     <row r="581" spans="1:1">
       <c r="A581">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="582" spans="1:1">
       <c r="A582">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="583" spans="1:1">
       <c r="A583">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="584" spans="1:1">
@@ -3459,17 +3459,17 @@
     </row>
     <row r="617" spans="1:1">
       <c r="A617">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="618" spans="1:1">
       <c r="A618">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="619" spans="1:1">
       <c r="A619">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="620" spans="1:1">
@@ -3819,17 +3819,17 @@
     </row>
     <row r="689" spans="1:1">
       <c r="A689">
-        <v>-1</v>
+        <v>1.407745272749739</v>
       </c>
     </row>
     <row r="690" spans="1:1">
       <c r="A690">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="691" spans="1:1">
       <c r="A691">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="692" spans="1:1">
@@ -4404,17 +4404,17 @@
     </row>
     <row r="806" spans="1:1">
       <c r="A806">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="807" spans="1:1">
       <c r="A807">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="808" spans="1:1">
       <c r="A808">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="809" spans="1:1">
@@ -4584,17 +4584,17 @@
     </row>
     <row r="842" spans="1:1">
       <c r="A842">
-        <v>-1</v>
+        <v>1.407745272749683</v>
       </c>
     </row>
     <row r="843" spans="1:1">
       <c r="A843">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="844" spans="1:1">
       <c r="A844">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845" spans="1:1">
@@ -6144,32 +6144,32 @@
     </row>
     <row r="1154" spans="1:1">
       <c r="A1154">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="1155" spans="1:1">
       <c r="A1155">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1156" spans="1:1">
       <c r="A1156">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1157" spans="1:1">
       <c r="A1157">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1158" spans="1:1">
       <c r="A1158">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1159" spans="1:1">
       <c r="A1159">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1160" spans="1:1">
@@ -9039,17 +9039,17 @@
     </row>
     <row r="1733" spans="1:1">
       <c r="A1733">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1734" spans="1:1">
       <c r="A1734">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1735" spans="1:1">
       <c r="A1735">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1736" spans="1:1">
@@ -12159,17 +12159,17 @@
     </row>
     <row r="2357" spans="1:1">
       <c r="A2357">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2358" spans="1:1">
       <c r="A2358">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2359" spans="1:1">
       <c r="A2359">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2360" spans="1:1">
@@ -23439,17 +23439,17 @@
     </row>
     <row r="4613" spans="1:1">
       <c r="A4613">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4614" spans="1:1">
       <c r="A4614">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4615" spans="1:1">
       <c r="A4615">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4616" spans="1:1">
@@ -34944,17 +34944,17 @@
     </row>
     <row r="6914" spans="1:1">
       <c r="A6914">
-        <v>-1</v>
+        <v>1.127766143616082</v>
       </c>
     </row>
     <row r="6915" spans="1:1">
       <c r="A6915">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6916" spans="1:1">
       <c r="A6916">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6917" spans="1:1">
@@ -36384,17 +36384,17 @@
     </row>
     <row r="7202" spans="1:1">
       <c r="A7202">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="7203" spans="1:1">
       <c r="A7203">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7204" spans="1:1">
       <c r="A7204">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7205" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -474,17 +474,17 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -924,17 +924,17 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -1014,17 +1014,17 @@
     </row>
     <row r="128" spans="1:1">
       <c r="A128">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -1134,17 +1134,17 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152">
-        <v>-1</v>
+        <v>2.416593574757864</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:1">
@@ -1539,17 +1539,17 @@
     </row>
     <row r="233" spans="1:1">
       <c r="A233">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="236" spans="1:1">
@@ -3294,17 +3294,17 @@
     </row>
     <row r="584" spans="1:1">
       <c r="A584">
-        <v>-1</v>
+        <v>2.422732887318002</v>
       </c>
     </row>
     <row r="585" spans="1:1">
       <c r="A585">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="586" spans="1:1">
       <c r="A586">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="587" spans="1:1">
@@ -3459,17 +3459,17 @@
     </row>
     <row r="617" spans="1:1">
       <c r="A617">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="618" spans="1:1">
       <c r="A618">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="619" spans="1:1">
       <c r="A619">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="620" spans="1:1">
@@ -3624,17 +3624,17 @@
     </row>
     <row r="650" spans="1:1">
       <c r="A650">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="651" spans="1:1">
       <c r="A651">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="652" spans="1:1">
       <c r="A652">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="653" spans="1:1">
@@ -3819,17 +3819,17 @@
     </row>
     <row r="689" spans="1:1">
       <c r="A689">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="690" spans="1:1">
       <c r="A690">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="691" spans="1:1">
       <c r="A691">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="692" spans="1:1">
@@ -3894,17 +3894,17 @@
     </row>
     <row r="704" spans="1:1">
       <c r="A704">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="705" spans="1:1">
       <c r="A705">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="706" spans="1:1">
       <c r="A706">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="707" spans="1:1">
@@ -4404,17 +4404,17 @@
     </row>
     <row r="806" spans="1:1">
       <c r="A806">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="807" spans="1:1">
       <c r="A807">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="808" spans="1:1">
       <c r="A808">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="809" spans="1:1">
@@ -4584,17 +4584,17 @@
     </row>
     <row r="842" spans="1:1">
       <c r="A842">
-        <v>1.407745272749683</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="843" spans="1:1">
       <c r="A843">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="844" spans="1:1">
       <c r="A844">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="845" spans="1:1">
@@ -7584,17 +7584,17 @@
     </row>
     <row r="1442" spans="1:1">
       <c r="A1442">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="1443" spans="1:1">
       <c r="A1443">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1444" spans="1:1">
       <c r="A1444">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1445" spans="1:1">
@@ -24159,17 +24159,17 @@
     </row>
     <row r="4757" spans="1:1">
       <c r="A4757">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="4758" spans="1:1">
       <c r="A4758">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4759" spans="1:1">
       <c r="A4759">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4760" spans="1:1">
@@ -24864,17 +24864,17 @@
     </row>
     <row r="4898" spans="1:1">
       <c r="A4898">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4899" spans="1:1">
       <c r="A4899">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4900" spans="1:1">
       <c r="A4900">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4901" spans="1:1">
@@ -34944,17 +34944,17 @@
     </row>
     <row r="6914" spans="1:1">
       <c r="A6914">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6915" spans="1:1">
       <c r="A6915">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6916" spans="1:1">
       <c r="A6916">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6917" spans="1:1">
@@ -34989,17 +34989,17 @@
     </row>
     <row r="6923" spans="1:1">
       <c r="A6923">
-        <v>-1</v>
+        <v>1.127766143616005</v>
       </c>
     </row>
     <row r="6924" spans="1:1">
       <c r="A6924">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6925" spans="1:1">
       <c r="A6925">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6926" spans="1:1">
@@ -35724,17 +35724,17 @@
     </row>
     <row r="7070" spans="1:1">
       <c r="A7070">
-        <v>-1</v>
+        <v>1.407745272749727</v>
       </c>
     </row>
     <row r="7071" spans="1:1">
       <c r="A7071">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7072" spans="1:1">
       <c r="A7072">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7073" spans="1:1">
@@ -36384,17 +36384,17 @@
     </row>
     <row r="7202" spans="1:1">
       <c r="A7202">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7203" spans="1:1">
       <c r="A7203">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7204" spans="1:1">
       <c r="A7204">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7205" spans="1:1">
@@ -42189,17 +42189,17 @@
     </row>
     <row r="8363" spans="1:1">
       <c r="A8363">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="8364" spans="1:1">
       <c r="A8364">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8365" spans="1:1">
       <c r="A8365">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8366" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -579,17 +579,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -744,17 +744,17 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>-1</v>
+        <v>1.127766143616094</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -924,17 +924,17 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -1014,17 +1014,17 @@
     </row>
     <row r="128" spans="1:1">
       <c r="A128">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -3294,17 +3294,17 @@
     </row>
     <row r="584" spans="1:1">
       <c r="A584">
-        <v>2.422732887318002</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="585" spans="1:1">
       <c r="A585">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="586" spans="1:1">
       <c r="A586">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="587" spans="1:1">
@@ -3624,17 +3624,17 @@
     </row>
     <row r="650" spans="1:1">
       <c r="A650">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="651" spans="1:1">
       <c r="A651">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="652" spans="1:1">
       <c r="A652">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="653" spans="1:1">
@@ -3894,17 +3894,17 @@
     </row>
     <row r="704" spans="1:1">
       <c r="A704">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="705" spans="1:1">
       <c r="A705">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="706" spans="1:1">
       <c r="A706">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="707" spans="1:1">
@@ -4719,17 +4719,17 @@
     </row>
     <row r="869" spans="1:1">
       <c r="A869">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="870" spans="1:1">
       <c r="A870">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="871" spans="1:1">
       <c r="A871">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="872" spans="1:1">
@@ -4809,17 +4809,17 @@
     </row>
     <row r="887" spans="1:1">
       <c r="A887">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="888" spans="1:1">
       <c r="A888">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="889" spans="1:1">
       <c r="A889">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="890" spans="1:1">
@@ -6144,17 +6144,17 @@
     </row>
     <row r="1154" spans="1:1">
       <c r="A1154">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1155" spans="1:1">
       <c r="A1155">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1156" spans="1:1">
       <c r="A1156">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1157" spans="1:1">
@@ -6504,17 +6504,17 @@
     </row>
     <row r="1226" spans="1:1">
       <c r="A1226">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="1227" spans="1:1">
       <c r="A1227">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1228" spans="1:1">
       <c r="A1228">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1229" spans="1:1">
@@ -6549,17 +6549,17 @@
     </row>
     <row r="1235" spans="1:1">
       <c r="A1235">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="1236" spans="1:1">
       <c r="A1236">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1237" spans="1:1">
       <c r="A1237">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1238" spans="1:1">
@@ -7584,17 +7584,17 @@
     </row>
     <row r="1442" spans="1:1">
       <c r="A1442">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1443" spans="1:1">
       <c r="A1443">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1444" spans="1:1">
       <c r="A1444">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1445" spans="1:1">
@@ -9519,17 +9519,17 @@
     </row>
     <row r="1829" spans="1:1">
       <c r="A1829">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="1830" spans="1:1">
       <c r="A1830">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1831" spans="1:1">
       <c r="A1831">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1832" spans="1:1">
@@ -10599,17 +10599,17 @@
     </row>
     <row r="2045" spans="1:1">
       <c r="A2045">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="2046" spans="1:1">
       <c r="A2046">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2047" spans="1:1">
       <c r="A2047">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2048" spans="1:1">
@@ -11919,17 +11919,17 @@
     </row>
     <row r="2309" spans="1:1">
       <c r="A2309">
-        <v>-1</v>
+        <v>1.407745272749761</v>
       </c>
     </row>
     <row r="2310" spans="1:1">
       <c r="A2310">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2311" spans="1:1">
       <c r="A2311">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2312" spans="1:1">
@@ -34959,17 +34959,17 @@
     </row>
     <row r="6917" spans="1:1">
       <c r="A6917">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="6918" spans="1:1">
       <c r="A6918">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6919" spans="1:1">
       <c r="A6919">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6920" spans="1:1">
@@ -34989,17 +34989,17 @@
     </row>
     <row r="6923" spans="1:1">
       <c r="A6923">
-        <v>1.127766143616005</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6924" spans="1:1">
       <c r="A6924">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6925" spans="1:1">
       <c r="A6925">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6926" spans="1:1">
@@ -35679,17 +35679,17 @@
     </row>
     <row r="7061" spans="1:1">
       <c r="A7061">
-        <v>-1</v>
+        <v>1.407745272749727</v>
       </c>
     </row>
     <row r="7062" spans="1:1">
       <c r="A7062">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7063" spans="1:1">
       <c r="A7063">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7064" spans="1:1">
@@ -35724,17 +35724,17 @@
     </row>
     <row r="7070" spans="1:1">
       <c r="A7070">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7071" spans="1:1">
       <c r="A7071">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7072" spans="1:1">
       <c r="A7072">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7073" spans="1:1">
@@ -42189,17 +42189,17 @@
     </row>
     <row r="8363" spans="1:1">
       <c r="A8363">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8364" spans="1:1">
       <c r="A8364">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8365" spans="1:1">
       <c r="A8365">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8366" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -579,17 +579,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -924,17 +924,17 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -1134,17 +1134,17 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152">
-        <v>2.416593574757864</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="155" spans="1:1">
@@ -1164,17 +1164,17 @@
     </row>
     <row r="158" spans="1:1">
       <c r="A158">
-        <v>-1</v>
+        <v>1.407745272749672</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:1">
@@ -1344,17 +1344,17 @@
     </row>
     <row r="194" spans="1:1">
       <c r="A194">
-        <v>-1</v>
+        <v>1.407745272749661</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:1">
@@ -1644,17 +1644,17 @@
     </row>
     <row r="254" spans="1:1">
       <c r="A254">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:1">
@@ -1824,17 +1824,17 @@
     </row>
     <row r="290" spans="1:1">
       <c r="A290">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:1">
@@ -3294,17 +3294,17 @@
     </row>
     <row r="584" spans="1:1">
       <c r="A584">
-        <v>-1</v>
+        <v>2.422732887318002</v>
       </c>
     </row>
     <row r="585" spans="1:1">
       <c r="A585">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="586" spans="1:1">
       <c r="A586">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="587" spans="1:1">
@@ -3384,17 +3384,17 @@
     </row>
     <row r="602" spans="1:1">
       <c r="A602">
-        <v>-1</v>
+        <v>2.422567290586075</v>
       </c>
     </row>
     <row r="603" spans="1:1">
       <c r="A603">
-        <v>-1</v>
+        <v>0.2877567709615669</v>
       </c>
     </row>
     <row r="604" spans="1:1">
       <c r="A604">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="605" spans="1:1">
@@ -4719,17 +4719,17 @@
     </row>
     <row r="869" spans="1:1">
       <c r="A869">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="870" spans="1:1">
       <c r="A870">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="871" spans="1:1">
       <c r="A871">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="872" spans="1:1">
@@ -4809,17 +4809,17 @@
     </row>
     <row r="887" spans="1:1">
       <c r="A887">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="888" spans="1:1">
       <c r="A888">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="889" spans="1:1">
       <c r="A889">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="890" spans="1:1">
@@ -6174,17 +6174,17 @@
     </row>
     <row r="1160" spans="1:1">
       <c r="A1160">
-        <v>-1</v>
+        <v>2.416593574757819</v>
       </c>
     </row>
     <row r="1161" spans="1:1">
       <c r="A1161">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1162" spans="1:1">
       <c r="A1162">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1163" spans="1:1">
@@ -6504,17 +6504,17 @@
     </row>
     <row r="1226" spans="1:1">
       <c r="A1226">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1227" spans="1:1">
       <c r="A1227">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1228" spans="1:1">
       <c r="A1228">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1229" spans="1:1">
@@ -6549,17 +6549,17 @@
     </row>
     <row r="1235" spans="1:1">
       <c r="A1235">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1236" spans="1:1">
       <c r="A1236">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1237" spans="1:1">
       <c r="A1237">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1238" spans="1:1">
@@ -9519,17 +9519,17 @@
     </row>
     <row r="1829" spans="1:1">
       <c r="A1829">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1830" spans="1:1">
       <c r="A1830">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1831" spans="1:1">
       <c r="A1831">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1832" spans="1:1">
@@ -10599,17 +10599,17 @@
     </row>
     <row r="2045" spans="1:1">
       <c r="A2045">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2046" spans="1:1">
       <c r="A2046">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2047" spans="1:1">
       <c r="A2047">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2048" spans="1:1">
@@ -11919,17 +11919,17 @@
     </row>
     <row r="2309" spans="1:1">
       <c r="A2309">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2310" spans="1:1">
       <c r="A2310">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2311" spans="1:1">
       <c r="A2311">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2312" spans="1:1">
@@ -17679,17 +17679,17 @@
     </row>
     <row r="3461" spans="1:1">
       <c r="A3461">
-        <v>-1</v>
+        <v>1.407745272749772</v>
       </c>
     </row>
     <row r="3462" spans="1:1">
       <c r="A3462">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3463" spans="1:1">
       <c r="A3463">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3464" spans="1:1">
@@ -23484,17 +23484,17 @@
     </row>
     <row r="4622" spans="1:1">
       <c r="A4622">
-        <v>-1</v>
+        <v>1.407745272749783</v>
       </c>
     </row>
     <row r="4623" spans="1:1">
       <c r="A4623">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4624" spans="1:1">
       <c r="A4624">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4625" spans="1:1">
@@ -24159,17 +24159,17 @@
     </row>
     <row r="4757" spans="1:1">
       <c r="A4757">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4758" spans="1:1">
       <c r="A4758">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4759" spans="1:1">
       <c r="A4759">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4760" spans="1:1">
@@ -34959,17 +34959,17 @@
     </row>
     <row r="6917" spans="1:1">
       <c r="A6917">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6918" spans="1:1">
       <c r="A6918">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6919" spans="1:1">
       <c r="A6919">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6920" spans="1:1">
@@ -35679,17 +35679,17 @@
     </row>
     <row r="7061" spans="1:1">
       <c r="A7061">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7062" spans="1:1">
       <c r="A7062">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7063" spans="1:1">
       <c r="A7063">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7064" spans="1:1">
@@ -40719,17 +40719,17 @@
     </row>
     <row r="8069" spans="1:1">
       <c r="A8069">
-        <v>-1</v>
+        <v>1.407745272749694</v>
       </c>
     </row>
     <row r="8070" spans="1:1">
       <c r="A8070">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8071" spans="1:1">
       <c r="A8071">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8072" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -444,17 +444,17 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -504,17 +504,17 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>-1</v>
+        <v>2.416593574757875</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>-1</v>
+        <v>0.2878201463827668</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -564,17 +564,17 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -744,32 +744,32 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>1.127766143616094</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -1164,17 +1164,17 @@
     </row>
     <row r="158" spans="1:1">
       <c r="A158">
-        <v>1.407745272749672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="161" spans="1:1">
@@ -1344,17 +1344,17 @@
     </row>
     <row r="194" spans="1:1">
       <c r="A194">
-        <v>1.407745272749661</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197" spans="1:1">
@@ -1644,17 +1644,17 @@
     </row>
     <row r="254" spans="1:1">
       <c r="A254">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="257" spans="1:1">
@@ -1824,17 +1824,17 @@
     </row>
     <row r="290" spans="1:1">
       <c r="A290">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="293" spans="1:1">
@@ -1914,17 +1914,17 @@
     </row>
     <row r="308" spans="1:1">
       <c r="A308">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:1">
@@ -2544,17 +2544,17 @@
     </row>
     <row r="434" spans="1:1">
       <c r="A434">
-        <v>-1</v>
+        <v>1.127766143616082</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437" spans="1:1">
@@ -3294,17 +3294,17 @@
     </row>
     <row r="584" spans="1:1">
       <c r="A584">
-        <v>2.422732887318002</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="585" spans="1:1">
       <c r="A585">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="586" spans="1:1">
       <c r="A586">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="587" spans="1:1">
@@ -3384,17 +3384,17 @@
     </row>
     <row r="602" spans="1:1">
       <c r="A602">
-        <v>2.422567290586075</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="603" spans="1:1">
       <c r="A603">
-        <v>0.2877567709615669</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="604" spans="1:1">
       <c r="A604">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="605" spans="1:1">
@@ -6174,17 +6174,17 @@
     </row>
     <row r="1160" spans="1:1">
       <c r="A1160">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1161" spans="1:1">
       <c r="A1161">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1162" spans="1:1">
       <c r="A1162">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1163" spans="1:1">
@@ -9744,17 +9744,17 @@
     </row>
     <row r="1874" spans="1:1">
       <c r="A1874">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="1875" spans="1:1">
       <c r="A1875">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1876" spans="1:1">
       <c r="A1876">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1877" spans="1:1">
@@ -11184,17 +11184,17 @@
     </row>
     <row r="2162" spans="1:1">
       <c r="A2162">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="2163" spans="1:1">
       <c r="A2163">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2164" spans="1:1">
       <c r="A2164">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2165" spans="1:1">
@@ -11934,17 +11934,17 @@
     </row>
     <row r="2312" spans="1:1">
       <c r="A2312">
-        <v>-1</v>
+        <v>2.416593574757886</v>
       </c>
     </row>
     <row r="2313" spans="1:1">
       <c r="A2313">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2314" spans="1:1">
       <c r="A2314">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2315" spans="1:1">
@@ -17679,17 +17679,17 @@
     </row>
     <row r="3461" spans="1:1">
       <c r="A3461">
-        <v>1.407745272749772</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3462" spans="1:1">
       <c r="A3462">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3463" spans="1:1">
       <c r="A3463">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3464" spans="1:1">
@@ -23439,17 +23439,17 @@
     </row>
     <row r="4613" spans="1:1">
       <c r="A4613">
-        <v>-1</v>
+        <v>1.407745272749739</v>
       </c>
     </row>
     <row r="4614" spans="1:1">
       <c r="A4614">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4615" spans="1:1">
       <c r="A4615">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4616" spans="1:1">
@@ -23484,17 +23484,17 @@
     </row>
     <row r="4622" spans="1:1">
       <c r="A4622">
-        <v>1.407745272749783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4623" spans="1:1">
       <c r="A4623">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4624" spans="1:1">
       <c r="A4624">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4625" spans="1:1">
@@ -32064,17 +32064,17 @@
     </row>
     <row r="6338" spans="1:1">
       <c r="A6338">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="6339" spans="1:1">
       <c r="A6339">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6340" spans="1:1">
       <c r="A6340">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6341" spans="1:1">
@@ -40719,17 +40719,17 @@
     </row>
     <row r="8069" spans="1:1">
       <c r="A8069">
-        <v>1.407745272749694</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8070" spans="1:1">
       <c r="A8070">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8071" spans="1:1">
       <c r="A8071">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8072" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -444,17 +444,17 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -474,17 +474,17 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -504,17 +504,17 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>2.416593574757875</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>0.2878201463827668</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:1">
@@ -564,17 +564,17 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -744,32 +744,32 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>-1</v>
+        <v>1.127766143616094</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -924,17 +924,17 @@
     </row>
     <row r="110" spans="1:1">
       <c r="A110">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="113" spans="1:1">
@@ -999,17 +999,17 @@
     </row>
     <row r="125" spans="1:1">
       <c r="A125">
-        <v>-1</v>
+        <v>2.416593574757808</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -1839,17 +1839,17 @@
     </row>
     <row r="293" spans="1:1">
       <c r="A293">
-        <v>-1</v>
+        <v>1.407745272749761</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:1">
@@ -2544,17 +2544,17 @@
     </row>
     <row r="434" spans="1:1">
       <c r="A434">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="437" spans="1:1">
@@ -3279,17 +3279,17 @@
     </row>
     <row r="581" spans="1:1">
       <c r="A581">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="582" spans="1:1">
       <c r="A582">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="583" spans="1:1">
       <c r="A583">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="584" spans="1:1">
@@ -6144,17 +6144,17 @@
     </row>
     <row r="1154" spans="1:1">
       <c r="A1154">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="1155" spans="1:1">
       <c r="A1155">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1156" spans="1:1">
       <c r="A1156">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1157" spans="1:1">
@@ -9744,17 +9744,17 @@
     </row>
     <row r="1874" spans="1:1">
       <c r="A1874">
-        <v>1.127766143616049</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1875" spans="1:1">
       <c r="A1875">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1876" spans="1:1">
       <c r="A1876">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1877" spans="1:1">
@@ -11184,17 +11184,17 @@
     </row>
     <row r="2162" spans="1:1">
       <c r="A2162">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2163" spans="1:1">
       <c r="A2163">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2164" spans="1:1">
       <c r="A2164">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2165" spans="1:1">
@@ -11934,17 +11934,17 @@
     </row>
     <row r="2312" spans="1:1">
       <c r="A2312">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2313" spans="1:1">
       <c r="A2313">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2314" spans="1:1">
       <c r="A2314">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2315" spans="1:1">
@@ -15519,17 +15519,17 @@
     </row>
     <row r="3029" spans="1:1">
       <c r="A3029">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="3030" spans="1:1">
       <c r="A3030">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3031" spans="1:1">
       <c r="A3031">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3032" spans="1:1">
@@ -23439,17 +23439,17 @@
     </row>
     <row r="4613" spans="1:1">
       <c r="A4613">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4614" spans="1:1">
       <c r="A4614">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4615" spans="1:1">
       <c r="A4615">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4616" spans="1:1">
@@ -24039,17 +24039,17 @@
     </row>
     <row r="4733" spans="1:1">
       <c r="A4733">
-        <v>-1</v>
+        <v>2.41659357475783</v>
       </c>
     </row>
     <row r="4734" spans="1:1">
       <c r="A4734">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4735" spans="1:1">
       <c r="A4735">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4736" spans="1:1">
@@ -32064,17 +32064,17 @@
     </row>
     <row r="6338" spans="1:1">
       <c r="A6338">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6339" spans="1:1">
       <c r="A6339">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6340" spans="1:1">
       <c r="A6340">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6341" spans="1:1">
@@ -35694,17 +35694,17 @@
     </row>
     <row r="7064" spans="1:1">
       <c r="A7064">
-        <v>-1</v>
+        <v>2.416593574757853</v>
       </c>
     </row>
     <row r="7065" spans="1:1">
       <c r="A7065">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7066" spans="1:1">
       <c r="A7066">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7067" spans="1:1">
@@ -35919,17 +35919,17 @@
     </row>
     <row r="7109" spans="1:1">
       <c r="A7109">
-        <v>-1</v>
+        <v>2.416593574757897</v>
       </c>
     </row>
     <row r="7110" spans="1:1">
       <c r="A7110">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7111" spans="1:1">
       <c r="A7111">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7112" spans="1:1">
@@ -38559,17 +38559,17 @@
     </row>
     <row r="7637" spans="1:1">
       <c r="A7637">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="7638" spans="1:1">
       <c r="A7638">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7639" spans="1:1">
       <c r="A7639">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7640" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -474,17 +474,17 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -834,17 +834,17 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -999,17 +999,17 @@
     </row>
     <row r="125" spans="1:1">
       <c r="A125">
-        <v>2.416593574757808</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -1839,17 +1839,17 @@
     </row>
     <row r="293" spans="1:1">
       <c r="A293">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="296" spans="1:1">
@@ -1914,17 +1914,17 @@
     </row>
     <row r="308" spans="1:1">
       <c r="A308">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="311" spans="1:1">
@@ -6144,17 +6144,17 @@
     </row>
     <row r="1154" spans="1:1">
       <c r="A1154">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1155" spans="1:1">
       <c r="A1155">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1156" spans="1:1">
       <c r="A1156">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1157" spans="1:1">
@@ -6174,17 +6174,17 @@
     </row>
     <row r="1160" spans="1:1">
       <c r="A1160">
-        <v>-1</v>
+        <v>2.416593574757819</v>
       </c>
     </row>
     <row r="1161" spans="1:1">
       <c r="A1161">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1162" spans="1:1">
       <c r="A1162">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1163" spans="1:1">
@@ -6399,17 +6399,17 @@
     </row>
     <row r="1205" spans="1:1">
       <c r="A1205">
-        <v>-1</v>
+        <v>2.416593574757853</v>
       </c>
     </row>
     <row r="1206" spans="1:1">
       <c r="A1206">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1207" spans="1:1">
       <c r="A1207">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1208" spans="1:1">
@@ -6849,17 +6849,17 @@
     </row>
     <row r="1295" spans="1:1">
       <c r="A1295">
-        <v>-1</v>
+        <v>2.416593574757853</v>
       </c>
     </row>
     <row r="1296" spans="1:1">
       <c r="A1296">
-        <v>-1</v>
+        <v>0.2943927399925106</v>
       </c>
     </row>
     <row r="1297" spans="1:1">
       <c r="A1297">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1298" spans="1:1">
@@ -12639,17 +12639,17 @@
     </row>
     <row r="2453" spans="1:1">
       <c r="A2453">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="2454" spans="1:1">
       <c r="A2454">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2455" spans="1:1">
       <c r="A2455">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2456" spans="1:1">
@@ -15519,17 +15519,17 @@
     </row>
     <row r="3029" spans="1:1">
       <c r="A3029">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3030" spans="1:1">
       <c r="A3030">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3031" spans="1:1">
       <c r="A3031">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3032" spans="1:1">
@@ -23439,17 +23439,17 @@
     </row>
     <row r="4613" spans="1:1">
       <c r="A4613">
-        <v>-1</v>
+        <v>1.407745272749739</v>
       </c>
     </row>
     <row r="4614" spans="1:1">
       <c r="A4614">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4615" spans="1:1">
       <c r="A4615">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4616" spans="1:1">
@@ -24039,17 +24039,17 @@
     </row>
     <row r="4733" spans="1:1">
       <c r="A4733">
-        <v>2.41659357475783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4734" spans="1:1">
       <c r="A4734">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4735" spans="1:1">
       <c r="A4735">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4736" spans="1:1">
@@ -24894,17 +24894,17 @@
     </row>
     <row r="4904" spans="1:1">
       <c r="A4904">
-        <v>-1</v>
+        <v>2.416593574757819</v>
       </c>
     </row>
     <row r="4905" spans="1:1">
       <c r="A4905">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4906" spans="1:1">
       <c r="A4906">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4907" spans="1:1">
@@ -35679,32 +35679,32 @@
     </row>
     <row r="7061" spans="1:1">
       <c r="A7061">
-        <v>-1</v>
+        <v>1.407745272749727</v>
       </c>
     </row>
     <row r="7062" spans="1:1">
       <c r="A7062">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7063" spans="1:1">
       <c r="A7063">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7064" spans="1:1">
       <c r="A7064">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7065" spans="1:1">
       <c r="A7065">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7066" spans="1:1">
       <c r="A7066">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7067" spans="1:1">
@@ -35919,17 +35919,17 @@
     </row>
     <row r="7109" spans="1:1">
       <c r="A7109">
-        <v>2.416593574757897</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7110" spans="1:1">
       <c r="A7110">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7111" spans="1:1">
       <c r="A7111">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7112" spans="1:1">
@@ -38559,17 +38559,17 @@
     </row>
     <row r="7637" spans="1:1">
       <c r="A7637">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7638" spans="1:1">
       <c r="A7638">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7639" spans="1:1">
       <c r="A7639">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7640" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -444,17 +444,17 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -474,17 +474,17 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -744,17 +744,17 @@
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>1.127766143616094</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77" spans="1:1">
@@ -834,17 +834,17 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="95" spans="1:1">
@@ -1104,17 +1104,17 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:1">
@@ -1824,17 +1824,17 @@
     </row>
     <row r="290" spans="1:1">
       <c r="A290">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:1">
@@ -2034,17 +2034,17 @@
     </row>
     <row r="332" spans="1:1">
       <c r="A332">
-        <v>-1</v>
+        <v>2.416593574757886</v>
       </c>
     </row>
     <row r="333" spans="1:1">
       <c r="A333">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:1">
@@ -3279,17 +3279,17 @@
     </row>
     <row r="581" spans="1:1">
       <c r="A581">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="582" spans="1:1">
       <c r="A582">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="583" spans="1:1">
       <c r="A583">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="584" spans="1:1">
@@ -3624,17 +3624,17 @@
     </row>
     <row r="650" spans="1:1">
       <c r="A650">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="651" spans="1:1">
       <c r="A651">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="652" spans="1:1">
       <c r="A652">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="653" spans="1:1">
@@ -4344,17 +4344,17 @@
     </row>
     <row r="794" spans="1:1">
       <c r="A794">
-        <v>-1</v>
+        <v>1.127766143616016</v>
       </c>
     </row>
     <row r="795" spans="1:1">
       <c r="A795">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="796" spans="1:1">
       <c r="A796">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="797" spans="1:1">
@@ -6144,17 +6144,17 @@
     </row>
     <row r="1154" spans="1:1">
       <c r="A1154">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="1155" spans="1:1">
       <c r="A1155">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1156" spans="1:1">
       <c r="A1156">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1157" spans="1:1">
@@ -6174,17 +6174,17 @@
     </row>
     <row r="1160" spans="1:1">
       <c r="A1160">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1161" spans="1:1">
       <c r="A1161">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1162" spans="1:1">
       <c r="A1162">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1163" spans="1:1">
@@ -6234,17 +6234,17 @@
     </row>
     <row r="1172" spans="1:1">
       <c r="A1172">
-        <v>-1</v>
+        <v>1.127766143616082</v>
       </c>
     </row>
     <row r="1173" spans="1:1">
       <c r="A1173">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1174" spans="1:1">
       <c r="A1174">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1175" spans="1:1">
@@ -6399,17 +6399,17 @@
     </row>
     <row r="1205" spans="1:1">
       <c r="A1205">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1206" spans="1:1">
       <c r="A1206">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1207" spans="1:1">
       <c r="A1207">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1208" spans="1:1">
@@ -6849,17 +6849,17 @@
     </row>
     <row r="1295" spans="1:1">
       <c r="A1295">
-        <v>2.416593574757853</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1296" spans="1:1">
       <c r="A1296">
-        <v>0.2943927399925106</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1297" spans="1:1">
       <c r="A1297">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1298" spans="1:1">
@@ -11919,17 +11919,17 @@
     </row>
     <row r="2309" spans="1:1">
       <c r="A2309">
-        <v>-1</v>
+        <v>1.407745272749761</v>
       </c>
     </row>
     <row r="2310" spans="1:1">
       <c r="A2310">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2311" spans="1:1">
       <c r="A2311">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2312" spans="1:1">
@@ -12639,17 +12639,17 @@
     </row>
     <row r="2453" spans="1:1">
       <c r="A2453">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2454" spans="1:1">
       <c r="A2454">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2455" spans="1:1">
       <c r="A2455">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2456" spans="1:1">
@@ -23439,17 +23439,17 @@
     </row>
     <row r="4613" spans="1:1">
       <c r="A4613">
-        <v>1.407745272749739</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4614" spans="1:1">
       <c r="A4614">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4615" spans="1:1">
       <c r="A4615">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4616" spans="1:1">
@@ -23634,17 +23634,17 @@
     </row>
     <row r="4652" spans="1:1">
       <c r="A4652">
-        <v>-1</v>
+        <v>2.416593574757886</v>
       </c>
     </row>
     <row r="4653" spans="1:1">
       <c r="A4653">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4654" spans="1:1">
       <c r="A4654">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4655" spans="1:1">
@@ -24894,17 +24894,17 @@
     </row>
     <row r="4904" spans="1:1">
       <c r="A4904">
-        <v>2.416593574757819</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4905" spans="1:1">
       <c r="A4905">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4906" spans="1:1">
       <c r="A4906">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4907" spans="1:1">
@@ -25074,17 +25074,17 @@
     </row>
     <row r="4940" spans="1:1">
       <c r="A4940">
-        <v>-1</v>
+        <v>2.41659357475793</v>
       </c>
     </row>
     <row r="4941" spans="1:1">
       <c r="A4941">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4942" spans="1:1">
       <c r="A4942">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4943" spans="1:1">
@@ -34959,17 +34959,17 @@
     </row>
     <row r="6917" spans="1:1">
       <c r="A6917">
-        <v>-1</v>
+        <v>1.40774527274975</v>
       </c>
     </row>
     <row r="6918" spans="1:1">
       <c r="A6918">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6919" spans="1:1">
       <c r="A6919">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6920" spans="1:1">
@@ -35154,17 +35154,17 @@
     </row>
     <row r="6956" spans="1:1">
       <c r="A6956">
-        <v>-1</v>
+        <v>2.416593574757886</v>
       </c>
     </row>
     <row r="6957" spans="1:1">
       <c r="A6957">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6958" spans="1:1">
       <c r="A6958">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6959" spans="1:1">
@@ -35679,17 +35679,17 @@
     </row>
     <row r="7061" spans="1:1">
       <c r="A7061">
-        <v>1.407745272749727</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7062" spans="1:1">
       <c r="A7062">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7063" spans="1:1">
       <c r="A7063">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7064" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -429,32 +429,32 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -474,17 +474,17 @@
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -594,17 +594,17 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>-1</v>
+        <v>2.416593574757919</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -1104,17 +1104,17 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="149" spans="1:1">
@@ -1209,17 +1209,17 @@
     </row>
     <row r="167" spans="1:1">
       <c r="A167">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:1">
@@ -1299,17 +1299,17 @@
     </row>
     <row r="185" spans="1:1">
       <c r="A185">
-        <v>-1</v>
+        <v>1.407745272749716</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:1">
@@ -2034,17 +2034,17 @@
     </row>
     <row r="332" spans="1:1">
       <c r="A332">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="333" spans="1:1">
       <c r="A333">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="335" spans="1:1">
@@ -3624,17 +3624,17 @@
     </row>
     <row r="650" spans="1:1">
       <c r="A650">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="651" spans="1:1">
       <c r="A651">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="652" spans="1:1">
       <c r="A652">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="653" spans="1:1">
@@ -3654,17 +3654,17 @@
     </row>
     <row r="656" spans="1:1">
       <c r="A656">
-        <v>-1</v>
+        <v>2.42278354617208</v>
       </c>
     </row>
     <row r="657" spans="1:1">
       <c r="A657">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="658" spans="1:1">
       <c r="A658">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="659" spans="1:1">
@@ -4344,17 +4344,17 @@
     </row>
     <row r="794" spans="1:1">
       <c r="A794">
-        <v>1.127766143616016</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="795" spans="1:1">
       <c r="A795">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="796" spans="1:1">
       <c r="A796">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="797" spans="1:1">
@@ -5094,17 +5094,17 @@
     </row>
     <row r="944" spans="1:1">
       <c r="A944">
-        <v>-1</v>
+        <v>2.423047624044672</v>
       </c>
     </row>
     <row r="945" spans="1:1">
       <c r="A945">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="946" spans="1:1">
       <c r="A946">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="947" spans="1:1">
@@ -6144,17 +6144,17 @@
     </row>
     <row r="1154" spans="1:1">
       <c r="A1154">
-        <v>1.12776614361606</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1155" spans="1:1">
       <c r="A1155">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1156" spans="1:1">
       <c r="A1156">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1157" spans="1:1">
@@ -6234,17 +6234,17 @@
     </row>
     <row r="1172" spans="1:1">
       <c r="A1172">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1173" spans="1:1">
       <c r="A1173">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1174" spans="1:1">
       <c r="A1174">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="1175" spans="1:1">
@@ -11919,17 +11919,17 @@
     </row>
     <row r="2309" spans="1:1">
       <c r="A2309">
-        <v>1.407745272749761</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2310" spans="1:1">
       <c r="A2310">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2311" spans="1:1">
       <c r="A2311">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="2312" spans="1:1">
@@ -23634,17 +23634,17 @@
     </row>
     <row r="4652" spans="1:1">
       <c r="A4652">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4653" spans="1:1">
       <c r="A4653">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4654" spans="1:1">
       <c r="A4654">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4655" spans="1:1">
@@ -25074,17 +25074,17 @@
     </row>
     <row r="4940" spans="1:1">
       <c r="A4940">
-        <v>2.41659357475793</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4941" spans="1:1">
       <c r="A4941">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4942" spans="1:1">
       <c r="A4942">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4943" spans="1:1">
@@ -29184,17 +29184,17 @@
     </row>
     <row r="5762" spans="1:1">
       <c r="A5762">
-        <v>-1</v>
+        <v>1.127766143616082</v>
       </c>
     </row>
     <row r="5763" spans="1:1">
       <c r="A5763">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5764" spans="1:1">
       <c r="A5764">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5765" spans="1:1">
@@ -34959,17 +34959,17 @@
     </row>
     <row r="6917" spans="1:1">
       <c r="A6917">
-        <v>1.40774527274975</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6918" spans="1:1">
       <c r="A6918">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6919" spans="1:1">
       <c r="A6919">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6920" spans="1:1">
@@ -35154,17 +35154,17 @@
     </row>
     <row r="6956" spans="1:1">
       <c r="A6956">
-        <v>2.416593574757886</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6957" spans="1:1">
       <c r="A6957">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6958" spans="1:1">
       <c r="A6958">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6959" spans="1:1">
@@ -40704,17 +40704,17 @@
     </row>
     <row r="8066" spans="1:1">
       <c r="A8066">
-        <v>-1</v>
+        <v>1.127766143616027</v>
       </c>
     </row>
     <row r="8067" spans="1:1">
       <c r="A8067">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8068" spans="1:1">
       <c r="A8068">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8069" spans="1:1">
@@ -40794,17 +40794,17 @@
     </row>
     <row r="8084" spans="1:1">
       <c r="A8084">
-        <v>-1</v>
+        <v>1.127766143616038</v>
       </c>
     </row>
     <row r="8085" spans="1:1">
       <c r="A8085">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8086" spans="1:1">
       <c r="A8086">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8087" spans="1:1">
@@ -41529,17 +41529,17 @@
     </row>
     <row r="8231" spans="1:1">
       <c r="A8231">
-        <v>-1</v>
+        <v>1.407745272749783</v>
       </c>
     </row>
     <row r="8232" spans="1:1">
       <c r="A8232">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8233" spans="1:1">
       <c r="A8233">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8234" spans="1:1">

--- a/src/hash_table.xlsx
+++ b/src/hash_table.xlsx
@@ -429,17 +429,17 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -519,17 +519,17 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:1">
@@ -564,17 +564,17 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -594,17 +594,17 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>2.416593574757919</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -759,17 +759,17 @@
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:1">
@@ -1119,17 +1119,17 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149">
-        <v>-1</v>
+        <v>1.407745272749694</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:1">
@@ -1209,17 +1209,17 @@
     </row>
     <row r="167" spans="1:1">
       <c r="A167">
-        <v>1.407745272749705</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="170" spans="1:1">
@@ -1299,17 +1299,17 @@
     </row>
     <row r="185" spans="1:1">
       <c r="A185">
-        <v>1.407745272749716</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="188" spans="1:1">
@@ -1824,17 +1824,17 @@
     </row>
     <row r="290" spans="1:1">
       <c r="A290">
-        <v>1.127766143616071</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="293" spans="1:1">
@@ -1869,17 +1869,17 @@
     </row>
     <row r="299" spans="1:1">
       <c r="A299">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302" spans="1:1">
@@ -1959,17 +1959,17 @@
     </row>
     <row r="317" spans="1:1">
       <c r="A317">
-        <v>-1</v>
+        <v>1.127766143616082</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:1">
@@ -2004,17 +2004,17 @@
     </row>
     <row r="326" spans="1:1">
       <c r="A326">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:1">
@@ -3654,17 +3654,17 @@
     </row>
     <row r="656" spans="1:1">
       <c r="A656">
-        <v>2.42278354617208</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="657" spans="1:1">
       <c r="A657">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="658" spans="1:1">
       <c r="A658">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="659" spans="1:1">
@@ -5094,17 +5094,17 @@
     </row>
     <row r="944" spans="1:1">
       <c r="A944">
-        <v>2.423047624044672</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="945" spans="1:1">
       <c r="A945">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="946" spans="1:1">
       <c r="A946">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="947" spans="1:1">
@@ -6174,17 +6174,17 @@
     </row>
     <row r="1160" spans="1:1">
       <c r="A1160">
-        <v>-1</v>
+        <v>2.416593574757819</v>
       </c>
     </row>
     <row r="1161" spans="1:1">
       <c r="A1161">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1162" spans="1:1">
       <c r="A1162">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1163" spans="1:1">
@@ -6279,17 +6279,17 @@
     </row>
     <row r="1181" spans="1:1">
       <c r="A1181">
-        <v>-1</v>
+        <v>1.12776614361606</v>
       </c>
     </row>
     <row r="1182" spans="1:1">
       <c r="A1182">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1183" spans="1:1">
       <c r="A1183">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1184" spans="1:1">
@@ -9054,17 +9054,17 @@
     </row>
     <row r="1736" spans="1:1">
       <c r="A1736">
-        <v>-1</v>
+        <v>2.422760337640606</v>
       </c>
     </row>
     <row r="1737" spans="1:1">
       <c r="A1737">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1738" spans="1:1">
       <c r="A1738">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1739" spans="1:1">
@@ -14814,17 +14814,17 @@
     </row>
     <row r="2888" spans="1:1">
       <c r="A2888">
-        <v>-1</v>
+        <v>2.43014087832828</v>
       </c>
     </row>
     <row r="2889" spans="1:1">
       <c r="A2889">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2890" spans="1:1">
       <c r="A2890">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2891" spans="1:1">
@@ -15519,17 +15519,17 @@
     </row>
     <row r="3029" spans="1:1">
       <c r="A3029">
-        <v>-1</v>
+        <v>1.407745272749705</v>
       </c>
     </row>
     <row r="3030" spans="1:1">
       <c r="A3030">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3031" spans="1:1">
       <c r="A3031">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3032" spans="1:1">
@@ -23424,17 +23424,17 @@
     </row>
     <row r="4610" spans="1:1">
       <c r="A4610">
-        <v>-1</v>
+        <v>1.127766143616049</v>
       </c>
     </row>
     <row r="4611" spans="1:1">
       <c r="A4611">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4612" spans="1:1">
       <c r="A4612">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4613" spans="1:1">
@@ -23784,17 +23784,17 @@
     </row>
     <row r="4682" spans="1:1">
       <c r="A4682">
-        <v>-1</v>
+        <v>1.127766143616071</v>
       </c>
     </row>
     <row r="4683" spans="1:1">
       <c r="A4683">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4684" spans="1:1">
       <c r="A4684">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4685" spans="1:1">
@@ -29184,17 +29184,17 @@
     </row>
     <row r="5762" spans="1:1">
       <c r="A5762">
-        <v>1.127766143616082</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5763" spans="1:1">
       <c r="A5763">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5764" spans="1:1">
       <c r="A5764">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5765" spans="1:1">
@@ -40704,17 +40704,17 @@
     </row>
     <row r="8066" spans="1:1">
       <c r="A8066">
-        <v>1.127766143616027</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8067" spans="1:1">
       <c r="A8067">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8068" spans="1:1">
       <c r="A8068">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8069" spans="1:1">
@@ -40794,17 +40794,17 @@
     </row>
     <row r="8084" spans="1:1">
       <c r="A8084">
-        <v>1.127766143616038</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8085" spans="1:1">
       <c r="A8085">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8086" spans="1:1">
       <c r="A8086">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8087" spans="1:1">
@@ -41529,17 +41529,17 @@
     </row>
     <row r="8231" spans="1:1">
       <c r="A8231">
-        <v>1.407745272749783</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8232" spans="1:1">
       <c r="A8232">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8233" spans="1:1">
       <c r="A8233">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8234" spans="1:1">
